--- a/shadowedhistory/still-home/series_log.xlsx
+++ b/shadowedhistory/still-home/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -704,6 +704,336 @@
       <c r="M5" t="inlineStr">
         <is>
           <t>/home/runner/work/youtube-automation/youtube-automation/output/series/still-home/episodes/ep02/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-15 23:09</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/58f84e11e2d794e8f24643cce7c147e8_1789513775.mp4</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/still-home/episodes/ep03/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-15 23:13</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/26f1a9dcecc1d9ebd29c007a242923b6_1789513878.mp4</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/still-home/episodes/ep03/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-16 23:12</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/9c5f551af07c9ca441b619a615193375_0_1789600311.mp4</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/still-home/episodes/ep03/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-16 23:21</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>189.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.945</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/09f8b02bc33def65ef83f1837306efc5_0_1789600594.mp4</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/still-home/episodes/ep03/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-16 23:23</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/a397d0f5063edbec7ed33780a5c55f17_0_1789600999.mp4</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/still-home/episodes/ep03/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-16 23:26</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/3a8ecef34c44dcc4bd69c68936a3c01c_0_1789601151.mp4</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/still-home/episodes/ep03/shots/shot_04.mp4</t>
         </is>
       </c>
     </row>

--- a/shadowedhistory/still-home/series_log.xlsx
+++ b/shadowedhistory/still-home/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1037,6 +1037,269 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:22</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/still-home/episodes/ep04/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09-18 22:46</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/bb5b542e596be980fa203366f69c2273_0_1789771586.mp4</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/still-home/episodes/ep04/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-18 22:52</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>189.0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0.945</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/21e320e693ea71e126185bebbb8c4dfd_0_1789771710.mp4</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/still-home/episodes/ep04/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-18 22:54</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/b9932140ce718548c53c3916397de3c2_0_1789772019.mp4</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/still-home/episodes/ep04/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-18 22:57</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/8ad9bdb0bc35aae10957a01aac759825_0_1789772201.mp4</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/still-home/episodes/ep04/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shadowedhistory/still-home/series_log.xlsx
+++ b/shadowedhistory/still-home/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1300,6 +1300,391 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-19 22:30</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>189.0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0.945</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/fd3603d86dbd150687587f37b91b9601_0_1789856776.mp4</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/still-home/episodes/ep05/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-19 22:31</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/f4da8d1cbf0fc7aeaadd359dd2e82668_0_1789857080.mp4</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/still-home/episodes/ep05/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-19 22:36</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/01bc3e6bc552f14578935538998ccbe9_0_1789857175.mp4</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/still-home/episodes/ep05/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-20 18:13</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/3b74c90418eb5a02d9c4703877ba63ce_0_1789927998.mp4</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/still-home/episodes/ep05/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-20 18:15</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/5f88d756e66dd187de1e4257101ce432_0_1789928095.mp4</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/still-home/episodes/ep05/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-20 18:18</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/d75d2620c944a22515757a93bfec3807_0_1789928200.mp4</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/still-home/episodes/ep05/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-20 18:22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/fd111aa80778c74c8c074a2a520c1dcf_0_1789928406.mp4</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/still-home/episodes/ep05/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shadowedhistory/still-home/series_log.xlsx
+++ b/shadowedhistory/still-home/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1685,6 +1685,336 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:33</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/7e58e12275f14e259a9bbeba6c5d6a7e_0_1790033459.mp4</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/still-home/episodes/ep06/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:40</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/81bd55026bd5e766426b78797b39e3f8_0_1790034034.mp4</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/still-home/episodes/ep06/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-22 23:12</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/90ed846706bbd15e8d64082140eba773_0_1790118758.mp4</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/still-home/episodes/ep06/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-22 23:20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/e63d99d543cc1dcc8bbf4ec33ec4f092_0_1790118934.mp4</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/still-home/episodes/ep06/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-22 23:29</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>189.0</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>0.945</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/d403cebc8db5dbb61f1198b66188eedb_0_1790119438.mp4</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/still-home/episodes/ep06/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-22 23:36</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/c695f63d7dea368c2d831af2b5d2845d_0_1790120135.mp4</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/still-home/episodes/ep06/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shadowedhistory/still-home/series_log.xlsx
+++ b/shadowedhistory/still-home/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2015,6 +2015,226 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-23 23:05</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/d83d75283dd597f612e3dfe62095376d_0_1790204697.mp4</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/still-home/episodes/ep07/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-23 23:09</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/5915bfa6b31cd04fad8a519fa6a82cf5_0_1790204823.mp4</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/still-home/episodes/ep07/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-23 23:13</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/40bc571a0f7a2a7ee24f2ae0e6a7349d_0_1790205043.mp4</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/still-home/episodes/ep07/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-23 23:15</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/2017d3a4460927188067b2b9fc79deb2_0_1790205288.mp4</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/still-home/episodes/ep07/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shadowedhistory/still-home/series_log.xlsx
+++ b/shadowedhistory/still-home/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2235,6 +2235,281 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-24 22:02</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>189.0</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>0.945</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/b473b1e7753c6a8a1fc9e6f5671df535_0_1790287112.mp4</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/still-home/episodes/ep08/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-25 16:01</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/8fb0527dd09328402c2ed20d1efeba7e_0_1790352074.mp4</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/still-home/episodes/ep08/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-09-25 16:06</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>189.0</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>0.945</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/c6f835da13c8c626dc2ecc914128bfe7_0_1790352197.mp4</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/still-home/episodes/ep08/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-09-25 16:09</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/143b21267b4f758e90158225bc9433f6_0_1790352519.mp4</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/still-home/episodes/ep08/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-09-25 16:12</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/e2b500f600c34eb97ff671d0a7464939_0_1790352621.mp4</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/still-home/episodes/ep08/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shadowedhistory/still-home/series_log.xlsx
+++ b/shadowedhistory/still-home/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2510,6 +2510,226 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-28 23:56</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/9727cc7c46b9e90990a1462d9b8d1ea7_0_1790639764.mp4</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/still-home/episodes/ep09/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-09-28 23:59</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/4d03848e9702d291f46bd65122e01f29_0_1790639869.mp4</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/still-home/episodes/ep09/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-09-29 00:04</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/59e9081041f469c209e825ae91ec6189_0_1790640085.mp4</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/still-home/episodes/ep09/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-09-29 00:05</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/39a618b57d3da121f60a7f7671723280_0_1790640324.mp4</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/still-home/episodes/ep09/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shadowedhistory/still-home/series_log.xlsx
+++ b/shadowedhistory/still-home/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2730,6 +2730,226 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-30 17:12</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/73c793d5a69242c38d76f75fe51afa34_0_1790787795.mp4</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/still-home/episodes/ep10/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-09-30 17:17</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/f1699611437d420c1e1ca00fcbc929f3_0_1790788549.mp4</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/still-home/episodes/ep10/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-30 17:24</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/956e1ef1058a28b0fcd2f140599e76a3_0_1790788940.mp4</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/still-home/episodes/ep10/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-30 17:28</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/28c65270d3701f9ad37b0b50ade491e2_0_1790789241.mp4</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/still-home/episodes/ep10/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
